--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_399_R44.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_399_R44.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5091</v>
+        <v>7.5077</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7338</v>
+        <v>8.6677</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2247</v>
+        <v>-1.16</v>
       </c>
       <c r="G2" t="n">
         <v>0.9907</v>
@@ -610,13 +610,13 @@
         <v>3.4121</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2322</v>
+        <v>0.7663</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7305</v>
+        <v>1.6644</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9628</v>
+        <v>-0.8981</v>
       </c>
       <c r="V2" t="n">
         <v>2.3386</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. LESSORT</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9553</v>
+        <v>0.2882</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6771</v>
+        <v>0.8303</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.7218</v>
+        <v>-0.5421</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8885</v>
+        <v>4.0032</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.3341</v>
+        <v>3.9047</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4455</v>
+        <v>0.0985</v>
       </c>
       <c r="J3" t="n">
-        <v>1.211</v>
+        <v>5.3525</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1301</v>
+        <v>4.3304</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3411</v>
+        <v>1.0221</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0995</v>
+        <v>-1.3493</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.204</v>
+        <v>-0.4257</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8956</v>
+        <v>-0.9236</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8198</v>
+        <v>-2.7297</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1374</v>
+        <v>-5.6868</v>
       </c>
       <c r="R3" t="n">
         <v>2.9572</v>
       </c>
       <c r="S3" t="n">
-        <v>5.2944</v>
+        <v>0.1048</v>
       </c>
       <c r="T3" t="n">
-        <v>5.6034</v>
+        <v>1.1646</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3091</v>
+        <v>-1.0598</v>
       </c>
       <c r="V3" t="n">
-        <v>-3.2703</v>
+        <v>-1.0901</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.2703</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.2576</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6021</v>
+        <v>-0.3143</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6949</v>
+        <v>0.0567</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9749</v>
+        <v>-1.4938</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1603</v>
+        <v>-1.2463</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1854</v>
+        <v>-0.2475</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1766</v>
+        <v>0.4607</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4665</v>
+        <v>-0.4043</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2899</v>
+        <v>0.865</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2017</v>
+        <v>-1.9545</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6938</v>
+        <v>-0.842</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8956</v>
+        <v>-1.1124</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5923</v>
+        <v>0.4549</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.2747</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6824</v>
+        <v>2.7297</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3864</v>
+        <v>0.7812</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7003</v>
+        <v>1.4997</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3139</v>
+        <v>-0.7185</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8617</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8617</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. TOLIOPOULOS</t>
+          <t>M. LESSORT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5095</v>
+        <v>-0.3905</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7292999999999999</v>
+        <v>2.5252</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2198</v>
+        <v>-2.9157</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1667</v>
+        <v>-0.8885</v>
       </c>
       <c r="H5" t="n">
-        <v>2.469</v>
+        <v>-1.3341</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3023</v>
+        <v>0.4455</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6834</v>
+        <v>1.211</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8633</v>
+        <v>-0.1301</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1799</v>
+        <v>1.3411</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4832</v>
+        <v>-2.0995</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6057</v>
+        <v>-1.204</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1225</v>
+        <v>-0.8956</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1374</v>
+        <v>1.8198</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.9572</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5387999999999999</v>
+        <v>1.9486</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2753</v>
+        <v>2.4516</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2635</v>
+        <v>-0.503</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-3.2703</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-3.2703</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>V. TOLIOPOULOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6892</v>
+        <v>-0.3927</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0483</v>
+        <v>-0.6125</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3591</v>
+        <v>0.2198</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7779</v>
+        <v>1.1667</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6222</v>
+        <v>2.469</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1556</v>
+        <v>-1.3023</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.5392</v>
+        <v>0.6834</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.761</v>
+        <v>1.8633</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7782</v>
+        <v>-1.1799</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7614</v>
+        <v>0.4832</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1388</v>
+        <v>0.6057</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6226</v>
+        <v>-0.1225</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0886</v>
+        <v>-0.422</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4909</v>
+        <v>-0.1586</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4023</v>
+        <v>-0.2635</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>N. ROGKAVOPOULOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.931</v>
+        <v>-0.8297</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6646</v>
+        <v>-1.4661</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2665</v>
+        <v>0.6363</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4938</v>
+        <v>-0.9195</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2463</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2475</v>
+        <v>-0.298</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4607</v>
+        <v>-1.4302</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4043</v>
+        <v>-0.7265</v>
       </c>
       <c r="L7" t="n">
-        <v>0.865</v>
+        <v>-0.7037</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9545</v>
+        <v>0.5107</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.842</v>
+        <v>0.105</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1124</v>
+        <v>0.4057</v>
       </c>
       <c r="P7" t="n">
         <v>0.4549</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2747</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7297</v>
+        <v>0.4549</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1078</v>
+        <v>-0.3652</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1495</v>
+        <v>-0.0358</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0417</v>
+        <v>-0.3293</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0282</v>
+        <v>-0.9425</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4538</v>
+        <v>-1.3985</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5744</v>
+        <v>0.456</v>
       </c>
       <c r="G8" t="n">
-        <v>4.0032</v>
+        <v>-0.7779</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9047</v>
+        <v>-0.6222</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0985</v>
+        <v>-0.1556</v>
       </c>
       <c r="J8" t="n">
-        <v>5.3525</v>
+        <v>-1.5392</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3304</v>
+        <v>-0.761</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0221</v>
+        <v>-0.7782</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3493</v>
+        <v>0.7614</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4257</v>
+        <v>0.1388</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9236</v>
+        <v>0.6226</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.7297</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.6868</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9572</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2116</v>
+        <v>-0.1646</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1195</v>
+        <v>0.1407</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0921</v>
+        <v>-0.3053</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. ROGKAVOPOULOS</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.135</v>
+        <v>-1.3176</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.933</v>
+        <v>-0.3318</v>
       </c>
       <c r="F9" t="n">
-        <v>0.798</v>
+        <v>-0.9858</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9195</v>
+        <v>0.9749</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6215000000000001</v>
+        <v>2.1603</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.298</v>
+        <v>-1.1854</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4302</v>
+        <v>1.1766</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7265</v>
+        <v>1.4665</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7037</v>
+        <v>-0.2899</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5107</v>
+        <v>-0.2017</v>
       </c>
       <c r="N9" t="n">
-        <v>0.105</v>
+        <v>0.6938</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4057</v>
+        <v>-0.8956</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4549</v>
+        <v>-1.5923</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.2747</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4549</v>
+        <v>0.6824</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6705</v>
+        <v>0.1616</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5028</v>
+        <v>0.7664</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1677</v>
+        <v>-0.6048</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.8617</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.8617</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.824</v>
+        <v>-2.2263</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1982</v>
+        <v>-0.6652</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6258</v>
+        <v>-1.5612</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9447</v>
@@ -1234,13 +1234,13 @@
         <v>0.2275</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0167</v>
+        <v>-0.419</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5628</v>
+        <v>0.0958</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5795</v>
+        <v>-0.5148</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0901</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>N. HAYES-DAVIS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4949</v>
+        <v>-2.5162</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4919</v>
+        <v>-1.0586</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.003</v>
+        <v>-1.4576</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1637</v>
+        <v>-6.4166</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.7854</v>
+        <v>-1.2456</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6218</v>
+        <v>-5.171</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9236</v>
+        <v>-4.7177</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.0784</v>
+        <v>0.581</v>
       </c>
       <c r="L11" t="n">
-        <v>1.1548</v>
+        <v>-5.2986</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.24</v>
+        <v>-1.6989</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.707</v>
+        <v>-1.8265</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4669</v>
+        <v>0.1276</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4549</v>
+        <v>2.9572</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6824</v>
+        <v>2.9572</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8764</v>
+        <v>1.1016</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.431</v>
+        <v>1.4788</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4454</v>
+        <v>-0.3772</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.1583</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.1802</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.3386</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. HAYES-DAVIS</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7159</v>
+        <v>-2.8789</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.226</v>
+        <v>-2.9083</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4899</v>
+        <v>0.0293</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.4166</v>
+        <v>-2.1637</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2456</v>
+        <v>-3.7854</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.171</v>
+        <v>1.6218</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.7177</v>
+        <v>-1.9236</v>
       </c>
       <c r="K12" t="n">
-        <v>0.581</v>
+        <v>-3.0784</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.2986</v>
+        <v>1.1548</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6989</v>
+        <v>-0.24</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.8265</v>
+        <v>-0.707</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1276</v>
+        <v>0.4669</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9572</v>
+        <v>-0.4549</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R12" t="n">
-        <v>2.9572</v>
+        <v>0.6824</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.2604</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3114</v>
+        <v>0.1527</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4096</v>
+        <v>-0.4131</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1583</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.1802</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,43 +1423,43 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9561</v>
+        <v>-3.956100000000001</v>
       </c>
       <c r="E13" t="n">
         <v>3.2679</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.2241</v>
+        <v>-7.224299999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-6.469200000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>2.231499999999999</v>
+        <v>2.2315</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.700600000000001</v>
+        <v>-8.7006</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0871</v>
+        <v>2.087100000000001</v>
       </c>
       <c r="K13" t="n">
         <v>6.9481</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.860900000000001</v>
+        <v>-4.8609</v>
       </c>
       <c r="M13" t="n">
         <v>-8.5562</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.7165</v>
+        <v>-4.716499999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-3.8399</v>
       </c>
       <c r="P13" t="n">
-        <v>3.4121</v>
+        <v>3.412100000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.6484</v>
@@ -1468,13 +1468,13 @@
         <v>17.0606</v>
       </c>
       <c r="S13" t="n">
-        <v>3.232900000000001</v>
+        <v>3.2329</v>
       </c>
       <c r="T13" t="n">
-        <v>9.2202</v>
+        <v>9.2203</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.987600000000001</v>
+        <v>-5.9874</v>
       </c>
       <c r="V13" t="n">
         <v>-4.1319</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.0198</v>
+        <v>9.545999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>10.0013</v>
+        <v>10.3515</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9815</v>
+        <v>-0.8055</v>
       </c>
       <c r="G14" t="n">
         <v>9.828799999999999</v>
@@ -1546,13 +1546,13 @@
         <v>2.0473</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0321</v>
+        <v>-0.5059</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6347</v>
+        <v>0.9849</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.6669</v>
+        <v>-1.4908</v>
       </c>
       <c r="V14" t="n">
         <v>2.7253</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1996</v>
+        <v>3.0837</v>
       </c>
       <c r="E15" t="n">
-        <v>5.149</v>
+        <v>3.7482</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9494</v>
+        <v>-0.6645</v>
       </c>
       <c r="G15" t="n">
         <v>1.8619</v>
@@ -1624,13 +1624,13 @@
         <v>1.1374</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2475</v>
+        <v>0.1317</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0474</v>
+        <v>0.6466</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.5149</v>
       </c>
       <c r="V15" t="n">
         <v>1.0901</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9396</v>
+        <v>2.6783</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4171</v>
+        <v>1.6506</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5225</v>
+        <v>1.0278</v>
       </c>
       <c r="G16" t="n">
         <v>3.6421</v>
@@ -1702,13 +1702,13 @@
         <v>1.3648</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7926</v>
+        <v>-0.0539</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2755</v>
+        <v>0.5089</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0681</v>
+        <v>-0.5628</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.248</v>
+        <v>2.1297</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5089</v>
+        <v>2.3261</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.261</v>
+        <v>-0.1963</v>
       </c>
       <c r="G17" t="n">
         <v>1.4443</v>
@@ -1780,13 +1780,13 @@
         <v>0.2275</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4238</v>
+        <v>0.4579</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2035</v>
+        <v>0.6137</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2204</v>
+        <v>-0.1557</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8147</v>
+        <v>1.0284</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.9449</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0135</v>
+        <v>0.0835</v>
       </c>
       <c r="G18" t="n">
         <v>1.217</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4023</v>
+        <v>-0.1886</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.1167</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4023</v>
+        <v>-0.3053</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2109</v>
+        <v>0.5803</v>
       </c>
       <c r="E19" t="n">
-        <v>0.365</v>
+        <v>0.4818</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1541</v>
+        <v>0.0985</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6143</v>
@@ -1936,13 +1936,13 @@
         <v>1.3648</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6298</v>
+        <v>-0.2604</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2753</v>
+        <v>-0.1586</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3545</v>
+        <v>-0.1018</v>
       </c>
       <c r="V19" t="n">
         <v>1.0901</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5384</v>
+        <v>0.098</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9571</v>
+        <v>-1.3734</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4187</v>
+        <v>1.4715</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1228</v>
@@ -2014,13 +2014,13 @@
         <v>1.8198</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3937</v>
+        <v>-0.7573</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0119</v>
+        <v>0.5718</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3819</v>
+        <v>-1.3291</v>
       </c>
       <c r="V20" t="n">
         <v>0.1583</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5891</v>
+        <v>-2.4724</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6429</v>
+        <v>-2.5262</v>
       </c>
       <c r="F21" t="n">
         <v>0.0538</v>
@@ -2092,10 +2092,10 @@
         <v>0.6824</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0598</v>
+        <v>0.1766</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1437</v>
+        <v>-0.0269</v>
       </c>
       <c r="U21" t="n">
         <v>0.2035</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9838</v>
+        <v>-2.6923</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4846</v>
+        <v>-1.6014</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4992</v>
+        <v>-1.0909</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5091</v>
@@ -2170,13 +2170,13 @@
         <v>0.9099</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2945</v>
+        <v>-0.003</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.7215</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1327</v>
+        <v>-0.7244</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0901</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4679</v>
+        <v>-3.6114</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8246</v>
+        <v>-4.7077</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6434</v>
+        <v>1.0963</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4213</v>
+        <v>-4.0966</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1919</v>
+        <v>-3.6231</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2293</v>
+        <v>-0.4736</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3549</v>
+        <v>-3.6967</v>
       </c>
       <c r="K23" t="n">
-        <v>0.719</v>
+        <v>-1.8171</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.0739</v>
+        <v>-1.8795</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0663</v>
+        <v>-0.4</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.9109</v>
+        <v>-1.8059</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8446</v>
+        <v>1.406</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6824</v>
+        <v>-0.9099</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2747</v>
+        <v>-3.4121</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5923</v>
+        <v>2.5022</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5675</v>
+        <v>0.1467</v>
       </c>
       <c r="T23" t="n">
-        <v>1.5566</v>
+        <v>1.1526</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9891</v>
+        <v>-1.0059</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9318</v>
+        <v>1.2485</v>
       </c>
       <c r="W23" t="n">
         <v>1.2485</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.897</v>
+        <v>-4.0774</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.591</v>
+        <v>-1.525</v>
       </c>
       <c r="F24" t="n">
-        <v>0.694</v>
+        <v>-2.5523</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.0966</v>
+        <v>-2.4213</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.6231</v>
+        <v>-1.1919</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4736</v>
+        <v>-1.2293</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.6967</v>
+        <v>-1.3549</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.8171</v>
+        <v>0.719</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.8795</v>
+        <v>-2.0739</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4</v>
+        <v>-1.0663</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.8059</v>
+        <v>-1.9109</v>
       </c>
       <c r="O24" t="n">
-        <v>1.406</v>
+        <v>0.8446</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9099</v>
+        <v>-0.6824</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4121</v>
+        <v>-2.2747</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5022</v>
+        <v>1.5923</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1389</v>
+        <v>-0.0419</v>
       </c>
       <c r="T24" t="n">
-        <v>1.2693</v>
+        <v>0.8562</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.4082</v>
+        <v>-0.8981</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2485</v>
+        <v>-0.9318</v>
       </c>
       <c r="W24" t="n">
         <v>1.2485</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-2.1802</v>
       </c>
     </row>
     <row r="25">
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.956399999999999</v>
+        <v>6.290900000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>7.769200000000002</v>
+        <v>7.769399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.8131</v>
+        <v>-1.4781</v>
       </c>
       <c r="G25" t="n">
-        <v>6.4691</v>
+        <v>6.469099999999999</v>
       </c>
       <c r="H25" t="n">
         <v>-2.231799999999999</v>
@@ -2404,16 +2404,16 @@
         <v>13.6484</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.232899999999999</v>
+        <v>-0.8980999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>5.9873</v>
+        <v>5.9874</v>
       </c>
       <c r="U25" t="n">
-        <v>-9.220499999999999</v>
+        <v>-6.8853</v>
       </c>
       <c r="V25" t="n">
-        <v>4.132099999999999</v>
+        <v>4.1321</v>
       </c>
       <c r="W25" t="n">
         <v>10.2861</v>
